--- a/data/trans_orig/IP18B2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18B2-Edad-trans_orig.xlsx
@@ -3109,12 +3109,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5486,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5501,12 +5501,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>465</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -7633,12 +7633,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8669,12 +8669,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -9332,12 +9332,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -10240,12 +10240,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10325,12 +10325,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10918,12 +10918,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10988,12 +10988,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -11031,12 +11031,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11101,12 +11101,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11179,12 +11179,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11327,12 +11327,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -11709,12 +11709,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11724,12 +11724,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11779,12 +11779,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11794,12 +11794,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -11822,12 +11822,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11837,12 +11837,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11892,12 +11892,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -12387,12 +12387,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12457,12 +12457,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12472,12 +12472,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -15261,12 +15261,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15276,12 +15276,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -15522,12 +15522,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -15904,12 +15904,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15919,12 +15919,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -15974,12 +15974,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15989,12 +15989,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16052,12 +16052,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16087,12 +16087,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16102,12 +16102,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -16808,12 +16808,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -16823,12 +16823,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -16858,12 +16858,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -16893,12 +16893,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -17408,12 +17408,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -17423,12 +17423,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -17443,12 +17443,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -17458,12 +17458,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -17603,12 +17603,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -17618,12 +17618,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -17673,12 +17673,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -17688,12 +17688,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -17829,12 +17829,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17844,12 +17844,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17864,12 +17864,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -17879,12 +17879,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17899,12 +17899,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17914,12 +17914,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -17947,7 +17947,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -18316,12 +18316,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -18394,12 +18394,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -18409,39 +18409,39 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>43,49%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
           <t>5,6%</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>43,26%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>2819</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -18464,12 +18464,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -18479,12 +18479,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18625,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -18695,7 +18695,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -19147,7 +19147,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -19260,7 +19260,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -19785,12 +19785,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -19800,12 +19800,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -19820,12 +19820,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -19835,12 +19835,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -20015,12 +20015,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -20050,12 +20050,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -20065,12 +20065,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -20206,12 +20206,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -20221,12 +20221,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -20241,12 +20241,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -20256,12 +20256,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -20276,12 +20276,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -20291,12 +20291,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -20698,7 +20698,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -20728,12 +20728,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -20743,12 +20743,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -20771,12 +20771,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -20786,12 +20786,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -20841,12 +20841,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -20856,12 +20856,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -20974,7 +20974,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -21519,12 +21519,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -21534,12 +21534,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -21602,7 +21602,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21828,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -21941,7 +21941,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22019,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -22104,7 +22104,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -22127,12 +22127,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -22142,12 +22142,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -22162,47 +22162,47 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
+          <t>6618</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>17,28%</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>34,99%</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
           <t>6113</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>32,32%</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R86" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -22212,12 +22212,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -22357,12 +22357,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -22372,12 +22372,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -22392,12 +22392,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -22407,12 +22407,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -22442,12 +22442,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -22510,7 +22510,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -22545,7 +22545,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -22560,7 +22560,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -22583,12 +22583,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -22598,12 +22598,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -22618,12 +22618,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -22653,12 +22653,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -22668,12 +22668,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -22786,7 +22786,7 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -23035,12 +23035,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -23050,12 +23050,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -23105,12 +23105,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -23148,12 +23148,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -23163,12 +23163,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -23183,12 +23183,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -23198,12 +23198,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -23233,12 +23233,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -23301,7 +23301,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -23379,7 +23379,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -23449,7 +23449,7 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -23655,7 +23655,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -23826,12 +23826,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -23841,12 +23841,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -23896,12 +23896,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -23911,12 +23911,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -23939,12 +23939,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -23954,12 +23954,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -23974,12 +23974,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -23989,12 +23989,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -24024,12 +24024,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -24205,7 +24205,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -24353,7 +24353,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -24391,12 +24391,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -24406,12 +24406,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -24431,7 +24431,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -24461,12 +24461,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -24476,12 +24476,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -24504,12 +24504,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -24519,12 +24519,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -24539,12 +24539,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -24554,12 +24554,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -27378,12 +27378,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -27393,12 +27393,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -27413,12 +27413,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -27428,12 +27428,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -27569,12 +27569,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -27584,12 +27584,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -27639,12 +27639,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -27654,12 +27654,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -28096,7 +28096,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -28111,7 +28111,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -28139,7 +28139,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -28174,7 +28174,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -28287,7 +28287,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -28302,7 +28302,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -28322,7 +28322,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -28337,7 +28337,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -28365,7 +28365,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -28380,7 +28380,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -28817,7 +28817,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -28852,7 +28852,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -28882,12 +28882,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -28897,12 +28897,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -29241,7 +29241,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -29269,7 +29269,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -29319,7 +29319,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -29339,7 +29339,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -29354,7 +29354,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -29495,7 +29495,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -29510,7 +29510,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -29545,7 +29545,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -29565,7 +29565,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -29580,7 +29580,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -29775,7 +29775,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -29790,12 +29790,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -29805,12 +29805,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -29873,7 +29873,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -29888,7 +29888,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -29923,7 +29923,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -29946,12 +29946,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -29961,12 +29961,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -29986,7 +29986,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -30016,12 +30016,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -30031,12 +30031,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -30247,7 +30247,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -30262,7 +30262,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -30403,7 +30403,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -30418,7 +30418,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -30453,7 +30453,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -30468,12 +30468,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -30483,12 +30483,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -30516,7 +30516,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -30531,7 +30531,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -30551,7 +30551,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -30586,7 +30586,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -30601,7 +30601,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -30664,7 +30664,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -30699,7 +30699,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -31194,7 +31194,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -31264,7 +31264,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -31279,7 +31279,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -31307,7 +31307,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -31322,7 +31322,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -31342,7 +31342,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -31357,7 +31357,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -31372,12 +31372,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -31387,12 +31387,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -31646,7 +31646,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -31661,7 +31661,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -31731,7 +31731,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -31759,7 +31759,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -31774,7 +31774,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -31887,7 +31887,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -31942,7 +31942,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -31957,7 +31957,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -32172,7 +32172,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -32187,7 +32187,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -32300,7 +32300,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -32328,7 +32328,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -32343,7 +32343,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -32358,12 +32358,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -32373,12 +32373,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -32393,12 +32393,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -32408,12 +32408,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -32604,7 +32604,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -32624,7 +32624,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -32682,7 +32682,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -32702,7 +32702,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -32732,12 +32732,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -32747,12 +32747,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -32795,7 +32795,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -32865,7 +32865,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -32943,7 +32943,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -32963,7 +32963,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -33076,7 +33076,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -33189,7 +33189,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -33204,7 +33204,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -33699,7 +33699,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -33714,12 +33714,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -33729,12 +33729,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -33749,12 +33749,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -33764,12 +33764,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -33910,7 +33910,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -33945,7 +33945,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -33960,7 +33960,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -33980,7 +33980,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -33995,7 +33995,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -34023,7 +34023,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -34093,7 +34093,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -34249,7 +34249,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -34264,7 +34264,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -34279,12 +34279,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -34294,12 +34294,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -34314,12 +34314,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -34329,12 +34329,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -34474,12 +34474,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -34489,12 +34489,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -34509,12 +34509,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -34524,12 +34524,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -34544,12 +34544,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -34559,12 +34559,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -34627,7 +34627,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -34642,7 +34642,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -34662,7 +34662,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -34677,7 +34677,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -34700,12 +34700,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -34715,12 +34715,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -34735,12 +34735,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -34750,12 +34750,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -34770,12 +34770,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -34785,12 +34785,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -34931,7 +34931,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -34966,7 +34966,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -34981,7 +34981,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -35044,7 +35044,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -35079,7 +35079,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -35094,7 +35094,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -35109,12 +35109,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -35124,12 +35124,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -35152,12 +35152,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -35167,12 +35167,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -35207,7 +35207,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -35222,12 +35222,12 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -35237,12 +35237,12 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -35285,7 +35285,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -35300,12 +35300,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -35315,12 +35315,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -35335,12 +35335,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -35350,12 +35350,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -35413,12 +35413,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -35428,12 +35428,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -35448,12 +35448,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -35463,12 +35463,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -35511,7 +35511,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -35546,7 +35546,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -35561,12 +35561,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -35576,12 +35576,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -35943,12 +35943,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -35958,12 +35958,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -35983,7 +35983,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -36013,12 +36013,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -36028,12 +36028,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -36056,12 +36056,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -36071,12 +36071,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -36091,12 +36091,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -36106,12 +36106,12 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -36126,12 +36126,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -36141,12 +36141,12 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -36287,7 +36287,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -36302,7 +36302,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -36337,7 +36337,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -36372,7 +36372,7 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -36395,12 +36395,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -36410,12 +36410,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -36435,7 +36435,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -36465,12 +36465,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -36480,12 +36480,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -36513,7 +36513,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -36528,7 +36528,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -36598,7 +36598,7 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -36621,12 +36621,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -36636,12 +36636,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -36656,12 +36656,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -36671,12 +36671,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -36691,12 +36691,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -36706,12 +36706,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
